--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -1324,7 +1324,7 @@
     <t>0.1983,0.0022,0.1988,0.2212</t>
   </si>
   <si>
-    <t>0.6324,0.0048,0.0349,0.2751</t>
+    <t>0.6324,0.0048,0.0349,0.2750</t>
   </si>
   <si>
     <t>0.4966,0.0032,0.0289,0.4385</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -814,6 +814,9 @@
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
@@ -823,118 +826,121 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8912,0.0013,0.0103,0.0686</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8913,0.0013,0.0103,0.0685</t>
   </si>
   <si>
     <t>0.0060,0.0004,0.0022,0.9985</t>
   </si>
   <si>
-    <t>0.4894,0.0005,0.0039,0.6738</t>
-  </si>
-  <si>
-    <t>0.4188,0.0011,0.0142,0.6891</t>
-  </si>
-  <si>
-    <t>0.3031,0.0045,0.0688,0.4552</t>
-  </si>
-  <si>
-    <t>0.1116,0.0032,0.0510,0.7956</t>
-  </si>
-  <si>
-    <t>0.1673,0.0041,0.1030,0.5348</t>
-  </si>
-  <si>
-    <t>0.3686,0.0032,0.1441,0.1269</t>
-  </si>
-  <si>
-    <t>0.5709,0.0020,0.0088,0.3644</t>
-  </si>
-  <si>
-    <t>0.1811,0.0033,0.0238,0.8020</t>
-  </si>
-  <si>
-    <t>0.1109,0.0023,0.0941,0.5973</t>
-  </si>
-  <si>
-    <t>0.1619,0.0027,0.0873,0.5893</t>
-  </si>
-  <si>
-    <t>0.5148,0.0142,0.1012,0.3397</t>
-  </si>
-  <si>
-    <t>0.0471,0.1250,0.8843,0.0531</t>
-  </si>
-  <si>
-    <t>0.1300,0.0079,0.8304,0.0107</t>
-  </si>
-  <si>
-    <t>0.1077,0.0281,0.8111,0.0174</t>
-  </si>
-  <si>
-    <t>0.5636,0.0036,0.2274,0.0374</t>
-  </si>
-  <si>
-    <t>0.0079,0.9606,0.0593,0.0185</t>
-  </si>
-  <si>
-    <t>0.0048,0.9373,0.0273,0.1211</t>
-  </si>
-  <si>
-    <t>0.5720,0.1284,0.0057,0.0042</t>
-  </si>
-  <si>
-    <t>0.0112,0.8745,0.1000,0.1579</t>
+    <t>0.4899,0.0005,0.0039,0.6730</t>
+  </si>
+  <si>
+    <t>0.4191,0.0011,0.0142,0.6886</t>
+  </si>
+  <si>
+    <t>0.3032,0.0045,0.0690,0.4542</t>
+  </si>
+  <si>
+    <t>0.1117,0.0032,0.0511,0.7949</t>
+  </si>
+  <si>
+    <t>0.1673,0.0041,0.1034,0.5338</t>
+  </si>
+  <si>
+    <t>0.3689,0.0032,0.1443,0.1266</t>
+  </si>
+  <si>
+    <t>0.5712,0.0020,0.0088,0.3638</t>
+  </si>
+  <si>
+    <t>0.1811,0.0033,0.0239,0.8014</t>
+  </si>
+  <si>
+    <t>0.1112,0.0023,0.0941,0.5964</t>
+  </si>
+  <si>
+    <t>0.1621,0.0027,0.0875,0.5884</t>
+  </si>
+  <si>
+    <t>0.5153,0.0142,0.1013,0.3391</t>
+  </si>
+  <si>
+    <t>0.0470,0.1250,0.8845,0.0530</t>
+  </si>
+  <si>
+    <t>0.1301,0.0079,0.8303,0.0107</t>
+  </si>
+  <si>
+    <t>0.1077,0.0281,0.8112,0.0174</t>
+  </si>
+  <si>
+    <t>0.5639,0.0036,0.2275,0.0373</t>
+  </si>
+  <si>
+    <t>0.0079,0.9606,0.0594,0.0184</t>
+  </si>
+  <si>
+    <t>0.0048,0.9375,0.0274,0.1207</t>
+  </si>
+  <si>
+    <t>0.5724,0.1285,0.0057,0.0041</t>
+  </si>
+  <si>
+    <t>0.0113,0.8747,0.1002,0.1574</t>
   </si>
   <si>
     <t>0.0157,0.9843,0.0523,0.0002</t>
   </si>
   <si>
-    <t>0.6297,0.0019,0.1315,0.0798</t>
-  </si>
-  <si>
-    <t>0.3036,0.0282,0.5621,0.0559</t>
+    <t>0.6299,0.0019,0.1316,0.0796</t>
+  </si>
+  <si>
+    <t>0.3038,0.0282,0.5621,0.0558</t>
   </si>
   <si>
     <t>0.0451,0.0008,0.9611,0.0014</t>
   </si>
   <si>
-    <t>0.0441,0.0202,0.9220,0.0305</t>
-  </si>
-  <si>
-    <t>0.1259,0.0108,0.8122,0.0181</t>
-  </si>
-  <si>
-    <t>0.0550,0.0019,0.9371,0.0082</t>
+    <t>0.0441,0.0202,0.9220,0.0304</t>
+  </si>
+  <si>
+    <t>0.1257,0.0108,0.8126,0.0181</t>
+  </si>
+  <si>
+    <t>0.0549,0.0019,0.9372,0.0082</t>
   </si>
   <si>
     <t>0.0041,0.0008,0.9942,0.0039</t>
   </si>
   <si>
-    <t>0.6958,0.0718,0.0628,0.0909</t>
-  </si>
-  <si>
-    <t>0.8592,0.0052,0.0169,0.0697</t>
+    <t>0.6960,0.0719,0.0629,0.0907</t>
+  </si>
+  <si>
+    <t>0.8594,0.0052,0.0169,0.0696</t>
   </si>
   <si>
     <t>0.0024,0.0006,0.9897,0.0048</t>
   </si>
   <si>
-    <t>0.0243,0.3411,0.8612,0.0292</t>
-  </si>
-  <si>
-    <t>0.6812,0.0030,0.0730,0.0817</t>
-  </si>
-  <si>
-    <t>0.7393,0.0144,0.0970,0.0514</t>
-  </si>
-  <si>
-    <t>0.5427,0.2854,0.0286,0.0133</t>
-  </si>
-  <si>
-    <t>0.2353,0.4424,0.1115,0.0216</t>
-  </si>
-  <si>
-    <t>0.0011,0.5860,0.9770,0.0003</t>
+    <t>0.0243,0.3411,0.8611,0.0291</t>
+  </si>
+  <si>
+    <t>0.6815,0.0030,0.0730,0.0815</t>
+  </si>
+  <si>
+    <t>0.7394,0.0144,0.0971,0.0512</t>
+  </si>
+  <si>
+    <t>0.5431,0.2857,0.0287,0.0133</t>
+  </si>
+  <si>
+    <t>0.2353,0.4428,0.1117,0.0216</t>
+  </si>
+  <si>
+    <t>0.0011,0.5859,0.9771,0.0003</t>
   </si>
   <si>
     <t>0.0014,0.0035,0.9969,0.0017</t>
@@ -943,7 +949,7 @@
     <t>0.0296,0.0198,0.9482,0.0173</t>
   </si>
   <si>
-    <t>0.4424,0.0011,0.4075,0.0244</t>
+    <t>0.4421,0.0011,0.4082,0.0243</t>
   </si>
   <si>
     <t>0.0018,0.5439,0.9671,0.0008</t>
@@ -952,7 +958,7 @@
     <t>0.0010,0.9858,0.0770,0.0026</t>
   </si>
   <si>
-    <t>0.0027,0.0195,0.9921,0.0046</t>
+    <t>0.0027,0.0195,0.9922,0.0046</t>
   </si>
   <si>
     <t>0.0048,0.0068,0.0082,0.9960</t>
@@ -973,37 +979,37 @@
     <t>0.0021,0.0417,0.9926,0.0015</t>
   </si>
   <si>
-    <t>0.0071,0.0046,0.9876,0.0072</t>
-  </si>
-  <si>
-    <t>0.0995,0.0003,0.9292,0.0006</t>
-  </si>
-  <si>
-    <t>0.0111,0.0064,0.9815,0.0088</t>
+    <t>0.0071,0.0046,0.9877,0.0071</t>
+  </si>
+  <si>
+    <t>0.0993,0.0003,0.9293,0.0006</t>
+  </si>
+  <si>
+    <t>0.0110,0.0064,0.9815,0.0088</t>
   </si>
   <si>
     <t>0.0106,0.0128,0.9767,0.0186</t>
   </si>
   <si>
-    <t>0.3145,0.0134,0.0690,0.4281</t>
-  </si>
-  <si>
-    <t>0.0874,0.0036,0.1934,0.5320</t>
-  </si>
-  <si>
-    <t>0.6235,0.0050,0.0367,0.2223</t>
-  </si>
-  <si>
-    <t>0.0357,0.0073,0.6946,0.1720</t>
-  </si>
-  <si>
-    <t>0.1779,0.0041,0.1603,0.3699</t>
-  </si>
-  <si>
-    <t>0.1114,0.0030,0.0598,0.7783</t>
-  </si>
-  <si>
-    <t>0.3916,0.0066,0.1486,0.1425</t>
+    <t>0.3147,0.0134,0.0692,0.4272</t>
+  </si>
+  <si>
+    <t>0.0876,0.0036,0.1936,0.5311</t>
+  </si>
+  <si>
+    <t>0.6240,0.0050,0.0367,0.2218</t>
+  </si>
+  <si>
+    <t>0.0357,0.0074,0.6951,0.1715</t>
+  </si>
+  <si>
+    <t>0.1781,0.0041,0.1605,0.3692</t>
+  </si>
+  <si>
+    <t>0.1114,0.0030,0.0599,0.7777</t>
+  </si>
+  <si>
+    <t>0.3918,0.0066,0.1487,0.1421</t>
   </si>
   <si>
     <t>0.0001,0.9860,0.9647,0.0000</t>
@@ -1021,7 +1027,7 @@
     <t>0.0001,0.0004,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0827,0.8915,0.0522,0.0020</t>
+    <t>0.0827,0.8916,0.0522,0.0020</t>
   </si>
   <si>
     <t>0.0009,0.9963,0.1152,0.0004</t>
@@ -1030,25 +1036,25 @@
     <t>0.9195,0.0084,0.0228,0.0352</t>
   </si>
   <si>
-    <t>0.3619,0.1097,0.1899,0.0795</t>
-  </si>
-  <si>
-    <t>0.0044,0.0696,0.9619,0.0740</t>
-  </si>
-  <si>
-    <t>0.0002,0.8972,0.9837,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.7307,0.9874,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9924,0.8714,0.0001</t>
+    <t>0.3620,0.1098,0.1901,0.0793</t>
+  </si>
+  <si>
+    <t>0.0044,0.0696,0.9619,0.0738</t>
+  </si>
+  <si>
+    <t>0.0002,0.8971,0.9837,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.7308,0.9874,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9924,0.8715,0.0001</t>
   </si>
   <si>
     <t>0.0004,0.8803,0.9768,0.0004</t>
   </si>
   <si>
-    <t>0.0045,0.0002,0.0069,0.9983</t>
+    <t>0.0045,0.0002,0.0070,0.9983</t>
   </si>
   <si>
     <t>0.0016,0.0002,0.0043,0.9994</t>
@@ -1057,7 +1063,7 @@
     <t>0.0032,0.0001,0.0027,0.9990</t>
   </si>
   <si>
-    <t>0.0032,0.0001,0.0113,0.9979</t>
+    <t>0.0032,0.0001,0.0114,0.9979</t>
   </si>
   <si>
     <t>0.0103,0.0004,0.0078,0.9960</t>
@@ -1072,7 +1078,7 @@
     <t>0.0006,0.5618,0.9917,0.0004</t>
   </si>
   <si>
-    <t>0.0012,0.7955,0.9565,0.0009</t>
+    <t>0.0012,0.7957,0.9565,0.0009</t>
   </si>
   <si>
     <t>0.0007,0.3311,0.9939,0.0004</t>
@@ -1081,103 +1087,103 @@
     <t>0.0001,0.9718,0.9861,0.0000</t>
   </si>
   <si>
-    <t>0.0012,0.8820,0.9353,0.0004</t>
-  </si>
-  <si>
-    <t>0.3870,0.0024,0.0210,0.5628</t>
-  </si>
-  <si>
-    <t>0.0996,0.0068,0.0750,0.7808</t>
-  </si>
-  <si>
-    <t>0.8482,0.0026,0.0061,0.0749</t>
-  </si>
-  <si>
-    <t>0.2003,0.0059,0.0305,0.7355</t>
-  </si>
-  <si>
-    <t>0.2498,0.0135,0.0679,0.5118</t>
-  </si>
-  <si>
-    <t>0.9069,0.0015,0.0061,0.0375</t>
-  </si>
-  <si>
-    <t>0.1254,0.0058,0.1194,0.6029</t>
+    <t>0.0012,0.8821,0.9353,0.0004</t>
+  </si>
+  <si>
+    <t>0.3875,0.0024,0.0211,0.5619</t>
+  </si>
+  <si>
+    <t>0.0997,0.0068,0.0752,0.7800</t>
+  </si>
+  <si>
+    <t>0.8484,0.0026,0.0061,0.0747</t>
+  </si>
+  <si>
+    <t>0.2007,0.0059,0.0306,0.7347</t>
+  </si>
+  <si>
+    <t>0.2502,0.0135,0.0680,0.5108</t>
+  </si>
+  <si>
+    <t>0.9069,0.0015,0.0061,0.0374</t>
+  </si>
+  <si>
+    <t>0.1255,0.0058,0.1197,0.6018</t>
   </si>
   <si>
     <t>0.9468,0.0017,0.0058,0.0006</t>
   </si>
   <si>
-    <t>0.1570,0.0022,0.0650,0.6721</t>
-  </si>
-  <si>
-    <t>0.8178,0.0027,0.0123,0.1088</t>
-  </si>
-  <si>
-    <t>0.0658,0.0017,0.0561,0.8575</t>
-  </si>
-  <si>
-    <t>0.6840,0.0018,0.0142,0.2549</t>
-  </si>
-  <si>
-    <t>0.2259,0.0018,0.0415,0.6213</t>
+    <t>0.1571,0.0022,0.0652,0.6713</t>
+  </si>
+  <si>
+    <t>0.8180,0.0027,0.0123,0.1085</t>
+  </si>
+  <si>
+    <t>0.0659,0.0017,0.0562,0.8570</t>
+  </si>
+  <si>
+    <t>0.6846,0.0018,0.0142,0.2541</t>
+  </si>
+  <si>
+    <t>0.2262,0.0018,0.0415,0.6203</t>
   </si>
   <si>
     <t>0.9508,0.0010,0.0038,0.0101</t>
   </si>
   <si>
-    <t>0.3286,0.0021,0.0185,0.6666</t>
-  </si>
-  <si>
-    <t>0.1983,0.0039,0.1010,0.4580</t>
+    <t>0.3287,0.0021,0.0185,0.6659</t>
+  </si>
+  <si>
+    <t>0.1988,0.0039,0.1011,0.4568</t>
   </si>
   <si>
     <t>0.0010,0.0006,0.9987,0.0004</t>
   </si>
   <si>
-    <t>0.2257,0.0144,0.7144,0.0204</t>
-  </si>
-  <si>
-    <t>0.9154,0.0012,0.0375,0.0087</t>
-  </si>
-  <si>
-    <t>0.0543,0.0043,0.9356,0.0065</t>
-  </si>
-  <si>
-    <t>0.0027,0.9898,0.0878,0.0136</t>
-  </si>
-  <si>
-    <t>0.0034,0.9920,0.0761,0.0038</t>
-  </si>
-  <si>
-    <t>0.5527,0.0821,0.0045,0.0163</t>
-  </si>
-  <si>
-    <t>0.1381,0.5422,0.0269,0.0422</t>
-  </si>
-  <si>
-    <t>0.0071,0.9867,0.0955,0.0040</t>
+    <t>0.2255,0.0144,0.7147,0.0203</t>
+  </si>
+  <si>
+    <t>0.9154,0.0012,0.0376,0.0087</t>
+  </si>
+  <si>
+    <t>0.0542,0.0043,0.9357,0.0065</t>
+  </si>
+  <si>
+    <t>0.0027,0.9898,0.0879,0.0135</t>
+  </si>
+  <si>
+    <t>0.0034,0.9921,0.0762,0.0038</t>
+  </si>
+  <si>
+    <t>0.5531,0.0823,0.0045,0.0162</t>
+  </si>
+  <si>
+    <t>0.1384,0.5425,0.0269,0.0420</t>
+  </si>
+  <si>
+    <t>0.0072,0.9867,0.0955,0.0040</t>
   </si>
   <si>
     <t>0.0003,0.9982,0.0345,0.0054</t>
   </si>
   <si>
-    <t>0.5935,0.1422,0.0237,0.0529</t>
-  </si>
-  <si>
-    <t>0.3777,0.0830,0.2878,0.1560</t>
-  </si>
-  <si>
-    <t>0.1270,0.0257,0.7293,0.0840</t>
-  </si>
-  <si>
-    <t>0.7269,0.0247,0.1954,0.0290</t>
-  </si>
-  <si>
-    <t>0.1621,0.0286,0.3831,0.4556</t>
-  </si>
-  <si>
-    <t>0.0239,0.0934,0.5675,0.3271</t>
+    <t>0.5938,0.1424,0.0238,0.0528</t>
+  </si>
+  <si>
+    <t>0.3780,0.0830,0.2879,0.1556</t>
+  </si>
+  <si>
+    <t>0.1269,0.0257,0.7294,0.0839</t>
+  </si>
+  <si>
+    <t>0.7269,0.0248,0.1955,0.0289</t>
+  </si>
+  <si>
+    <t>0.1620,0.0287,0.3837,0.4551</t>
+  </si>
+  <si>
+    <t>0.0239,0.0936,0.5679,0.3265</t>
   </si>
   <si>
     <t>0.0009,0.9985,0.0327,0.0001</t>
@@ -1186,67 +1192,67 @@
     <t>0.0003,0.9990,0.0154,0.0002</t>
   </si>
   <si>
-    <t>0.0010,0.9719,0.0389,0.2331</t>
-  </si>
-  <si>
-    <t>0.0007,0.9967,0.3044,0.0003</t>
-  </si>
-  <si>
-    <t>0.0186,0.9510,0.2084,0.0046</t>
-  </si>
-  <si>
-    <t>0.4344,0.1777,0.0890,0.0635</t>
-  </si>
-  <si>
-    <t>0.0782,0.5425,0.0614,0.1228</t>
-  </si>
-  <si>
-    <t>0.5887,0.0009,0.0162,0.4018</t>
-  </si>
-  <si>
-    <t>0.8093,0.0017,0.0074,0.1832</t>
-  </si>
-  <si>
-    <t>0.1612,0.0019,0.0323,0.8108</t>
-  </si>
-  <si>
-    <t>0.5111,0.0035,0.0368,0.3774</t>
-  </si>
-  <si>
-    <t>0.9254,0.0014,0.0056,0.0287</t>
-  </si>
-  <si>
-    <t>0.3119,0.0012,0.0391,0.5849</t>
-  </si>
-  <si>
-    <t>0.1009,0.0015,0.0842,0.6915</t>
-  </si>
-  <si>
-    <t>0.2767,0.0024,0.1348,0.2214</t>
-  </si>
-  <si>
-    <t>0.0018,0.5261,0.9732,0.0006</t>
+    <t>0.0010,0.9719,0.0390,0.2324</t>
+  </si>
+  <si>
+    <t>0.0007,0.9967,0.3045,0.0003</t>
+  </si>
+  <si>
+    <t>0.0187,0.9510,0.2085,0.0045</t>
+  </si>
+  <si>
+    <t>0.4347,0.1778,0.0891,0.0634</t>
+  </si>
+  <si>
+    <t>0.0784,0.5429,0.0615,0.1223</t>
+  </si>
+  <si>
+    <t>0.5890,0.0009,0.0162,0.4010</t>
+  </si>
+  <si>
+    <t>0.8096,0.0017,0.0074,0.1828</t>
+  </si>
+  <si>
+    <t>0.1613,0.0019,0.0324,0.8103</t>
+  </si>
+  <si>
+    <t>0.5114,0.0035,0.0369,0.3766</t>
+  </si>
+  <si>
+    <t>0.9255,0.0014,0.0056,0.0287</t>
+  </si>
+  <si>
+    <t>0.3123,0.0012,0.0391,0.5840</t>
+  </si>
+  <si>
+    <t>0.1010,0.0015,0.0845,0.6906</t>
+  </si>
+  <si>
+    <t>0.2772,0.0024,0.1349,0.2208</t>
+  </si>
+  <si>
+    <t>0.0018,0.5262,0.9732,0.0006</t>
   </si>
   <si>
     <t>0.0005,0.2340,0.9956,0.0001</t>
   </si>
   <si>
-    <t>0.0004,0.0267,0.9986,0.0003</t>
+    <t>0.0004,0.0266,0.9986,0.0003</t>
   </si>
   <si>
     <t>0.0101,0.0333,0.9814,0.0025</t>
   </si>
   <si>
-    <t>0.8998,0.0036,0.0201,0.0580</t>
-  </si>
-  <si>
-    <t>0.4266,0.0922,0.1967,0.2723</t>
-  </si>
-  <si>
-    <t>0.1538,0.0025,0.6497,0.0564</t>
-  </si>
-  <si>
-    <t>0.6958,0.0245,0.1253,0.1190</t>
+    <t>0.8999,0.0036,0.0201,0.0579</t>
+  </si>
+  <si>
+    <t>0.4269,0.0923,0.1969,0.2716</t>
+  </si>
+  <si>
+    <t>0.1537,0.0025,0.6502,0.0563</t>
+  </si>
+  <si>
+    <t>0.6960,0.0246,0.1253,0.1187</t>
   </si>
   <si>
     <t>0.0060,0.0001,0.0070,0.9971</t>
@@ -1258,25 +1264,25 @@
     <t>0.0005,0.0001,0.0034,0.9998</t>
   </si>
   <si>
-    <t>0.0048,0.0001,0.0054,0.9982</t>
+    <t>0.0048,0.0001,0.0055,0.9982</t>
   </si>
   <si>
     <t>0.0002,0.9579,0.9658,0.0001</t>
   </si>
   <si>
-    <t>0.2170,0.0027,0.0736,0.5625</t>
-  </si>
-  <si>
-    <t>0.0520,0.1735,0.1311,0.5189</t>
-  </si>
-  <si>
-    <t>0.4811,0.0024,0.0711,0.2308</t>
-  </si>
-  <si>
-    <t>0.0710,0.2759,0.1262,0.3353</t>
-  </si>
-  <si>
-    <t>0.7308,0.0015,0.0150,0.2506</t>
+    <t>0.2171,0.0027,0.0738,0.5619</t>
+  </si>
+  <si>
+    <t>0.0521,0.1738,0.1314,0.5180</t>
+  </si>
+  <si>
+    <t>0.4810,0.0024,0.0713,0.2302</t>
+  </si>
+  <si>
+    <t>0.0711,0.2763,0.1265,0.3346</t>
+  </si>
+  <si>
+    <t>0.7312,0.0015,0.0150,0.2500</t>
   </si>
   <si>
     <t>0.0282,0.0000,0.9772,0.0000</t>
@@ -1288,82 +1294,82 @@
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.4901,0.0003,0.3142,0.0028</t>
-  </si>
-  <si>
-    <t>0.7191,0.0035,0.0834,0.0483</t>
-  </si>
-  <si>
-    <t>0.6449,0.0600,0.0798,0.1015</t>
-  </si>
-  <si>
-    <t>0.8946,0.0056,0.0169,0.0796</t>
-  </si>
-  <si>
-    <t>0.7845,0.0150,0.0291,0.1592</t>
-  </si>
-  <si>
-    <t>0.2813,0.1578,0.0988,0.2112</t>
-  </si>
-  <si>
-    <t>0.6900,0.0141,0.0722,0.1665</t>
-  </si>
-  <si>
-    <t>0.8142,0.0298,0.0446,0.0667</t>
-  </si>
-  <si>
-    <t>0.4296,0.0031,0.0436,0.4044</t>
-  </si>
-  <si>
-    <t>0.8296,0.0006,0.0043,0.1436</t>
-  </si>
-  <si>
-    <t>0.3068,0.0047,0.0640,0.5035</t>
-  </si>
-  <si>
-    <t>0.1983,0.0022,0.1988,0.2212</t>
-  </si>
-  <si>
-    <t>0.6324,0.0048,0.0349,0.2750</t>
-  </si>
-  <si>
-    <t>0.4966,0.0032,0.0289,0.4385</t>
-  </si>
-  <si>
-    <t>0.1478,0.0032,0.0786,0.6992</t>
-  </si>
-  <si>
-    <t>0.0868,0.0019,0.1274,0.6309</t>
-  </si>
-  <si>
-    <t>0.4537,0.0475,0.0133,0.1170</t>
-  </si>
-  <si>
-    <t>0.6569,0.1112,0.0357,0.0424</t>
-  </si>
-  <si>
-    <t>0.7499,0.0654,0.0454,0.0614</t>
-  </si>
-  <si>
-    <t>0.2057,0.0120,0.2258,0.1849</t>
-  </si>
-  <si>
-    <t>0.3987,0.0120,0.0441,0.4270</t>
-  </si>
-  <si>
-    <t>0.2904,0.0329,0.2174,0.1660</t>
-  </si>
-  <si>
-    <t>0.3988,0.0072,0.0805,0.2982</t>
-  </si>
-  <si>
-    <t>0.2113,0.0118,0.0384,0.7328</t>
+    <t>0.4902,0.0003,0.3143,0.0028</t>
+  </si>
+  <si>
+    <t>0.7191,0.0035,0.0834,0.0482</t>
+  </si>
+  <si>
+    <t>0.6448,0.0601,0.0800,0.1013</t>
+  </si>
+  <si>
+    <t>0.8946,0.0056,0.0169,0.0795</t>
+  </si>
+  <si>
+    <t>0.7846,0.0150,0.0291,0.1588</t>
+  </si>
+  <si>
+    <t>0.2814,0.1581,0.0990,0.2107</t>
+  </si>
+  <si>
+    <t>0.6901,0.0141,0.0723,0.1661</t>
+  </si>
+  <si>
+    <t>0.8143,0.0299,0.0447,0.0665</t>
+  </si>
+  <si>
+    <t>0.4297,0.0031,0.0438,0.4036</t>
+  </si>
+  <si>
+    <t>0.8297,0.0006,0.0043,0.1433</t>
+  </si>
+  <si>
+    <t>0.3072,0.0047,0.0641,0.5026</t>
+  </si>
+  <si>
+    <t>0.1985,0.0022,0.1990,0.2207</t>
+  </si>
+  <si>
+    <t>0.6328,0.0048,0.0349,0.2744</t>
+  </si>
+  <si>
+    <t>0.4974,0.0032,0.0289,0.4375</t>
+  </si>
+  <si>
+    <t>0.1481,0.0032,0.0786,0.6985</t>
+  </si>
+  <si>
+    <t>0.0870,0.0019,0.1276,0.6299</t>
+  </si>
+  <si>
+    <t>0.4541,0.0476,0.0133,0.1167</t>
+  </si>
+  <si>
+    <t>0.6574,0.1113,0.0358,0.0423</t>
+  </si>
+  <si>
+    <t>0.7499,0.0655,0.0455,0.0613</t>
+  </si>
+  <si>
+    <t>0.2058,0.0121,0.2260,0.1845</t>
+  </si>
+  <si>
+    <t>0.3989,0.0120,0.0442,0.4263</t>
+  </si>
+  <si>
+    <t>0.2907,0.0329,0.2174,0.1656</t>
+  </si>
+  <si>
+    <t>0.3992,0.0072,0.0806,0.2976</t>
+  </si>
+  <si>
+    <t>0.2118,0.0118,0.0385,0.7318</t>
   </si>
   <si>
     <t>0.0027,0.0383,0.9840,0.0153</t>
   </si>
   <si>
-    <t>0.2552,0.0415,0.2731,0.1617</t>
+    <t>0.2554,0.0416,0.2733,0.1613</t>
   </si>
   <si>
     <t>0.0005,0.0021,0.9991,0.0002</t>
@@ -1372,13 +1378,13 @@
     <t>0.0012,0.1000,0.9910,0.0048</t>
   </si>
   <si>
-    <t>0.0768,0.0207,0.8043,0.0498</t>
-  </si>
-  <si>
-    <t>0.0019,0.0981,0.9885,0.0018</t>
-  </si>
-  <si>
-    <t>0.0022,0.0096,0.9951,0.0015</t>
+    <t>0.0767,0.0207,0.8046,0.0496</t>
+  </si>
+  <si>
+    <t>0.0019,0.0980,0.9885,0.0018</t>
+  </si>
+  <si>
+    <t>0.0022,0.0095,0.9951,0.0015</t>
   </si>
   <si>
     <t>0.0021,0.0008,0.9974,0.0005</t>
@@ -1387,67 +1393,67 @@
     <t>0.0121,0.0027,0.9866,0.0020</t>
   </si>
   <si>
-    <t>0.2128,0.0261,0.6966,0.0282</t>
-  </si>
-  <si>
-    <t>0.1589,0.0103,0.7675,0.0213</t>
-  </si>
-  <si>
-    <t>0.5341,0.1065,0.1768,0.1547</t>
-  </si>
-  <si>
-    <t>0.0347,0.0803,0.8665,0.1610</t>
-  </si>
-  <si>
-    <t>0.0209,0.1173,0.9410,0.0165</t>
-  </si>
-  <si>
-    <t>0.0942,0.0170,0.8421,0.0285</t>
-  </si>
-  <si>
-    <t>0.2408,0.0225,0.5587,0.0839</t>
-  </si>
-  <si>
-    <t>0.5015,0.0721,0.3186,0.0355</t>
-  </si>
-  <si>
-    <t>0.8223,0.0142,0.0073,0.0192</t>
-  </si>
-  <si>
-    <t>0.0623,0.4899,0.1059,0.1468</t>
-  </si>
-  <si>
-    <t>0.1617,0.1006,0.1108,0.3595</t>
-  </si>
-  <si>
-    <t>0.2184,0.0286,0.1766,0.2982</t>
-  </si>
-  <si>
-    <t>0.0963,0.0361,0.0680,0.7212</t>
-  </si>
-  <si>
-    <t>0.6141,0.2814,0.0575,0.0234</t>
-  </si>
-  <si>
-    <t>0.8511,0.0058,0.0125,0.1130</t>
-  </si>
-  <si>
-    <t>0.3662,0.0324,0.1747,0.3494</t>
-  </si>
-  <si>
-    <t>0.1563,0.0068,0.6988,0.0480</t>
-  </si>
-  <si>
-    <t>0.3988,0.0069,0.2465,0.1932</t>
-  </si>
-  <si>
-    <t>0.0117,0.0100,0.9650,0.0453</t>
-  </si>
-  <si>
-    <t>0.2383,0.0036,0.7350,0.0015</t>
-  </si>
-  <si>
-    <t>0.2021,0.0086,0.7644,0.0049</t>
+    <t>0.2126,0.0261,0.6970,0.0282</t>
+  </si>
+  <si>
+    <t>0.1589,0.0103,0.7676,0.0213</t>
+  </si>
+  <si>
+    <t>0.5340,0.1067,0.1770,0.1544</t>
+  </si>
+  <si>
+    <t>0.0347,0.0804,0.8667,0.1605</t>
+  </si>
+  <si>
+    <t>0.0209,0.1172,0.9410,0.0165</t>
+  </si>
+  <si>
+    <t>0.0942,0.0170,0.8423,0.0285</t>
+  </si>
+  <si>
+    <t>0.2406,0.0225,0.5593,0.0837</t>
+  </si>
+  <si>
+    <t>0.5015,0.0721,0.3187,0.0354</t>
+  </si>
+  <si>
+    <t>0.8225,0.0142,0.0073,0.0192</t>
+  </si>
+  <si>
+    <t>0.0623,0.4903,0.1061,0.1463</t>
+  </si>
+  <si>
+    <t>0.1618,0.1008,0.1110,0.3585</t>
+  </si>
+  <si>
+    <t>0.2186,0.0286,0.1770,0.2974</t>
+  </si>
+  <si>
+    <t>0.0965,0.0362,0.0682,0.7204</t>
+  </si>
+  <si>
+    <t>0.6140,0.2818,0.0575,0.0233</t>
+  </si>
+  <si>
+    <t>0.8511,0.0059,0.0126,0.1129</t>
+  </si>
+  <si>
+    <t>0.3660,0.0325,0.1752,0.3491</t>
+  </si>
+  <si>
+    <t>0.1561,0.0068,0.6993,0.0479</t>
+  </si>
+  <si>
+    <t>0.3989,0.0070,0.2469,0.1929</t>
+  </si>
+  <si>
+    <t>0.0117,0.0100,0.9650,0.0452</t>
+  </si>
+  <si>
+    <t>0.2381,0.0036,0.7353,0.0015</t>
+  </si>
+  <si>
+    <t>0.2019,0.0086,0.7647,0.0049</t>
   </si>
   <si>
     <t>0.0045,0.0145,0.9922,0.0019</t>
@@ -1456,37 +1462,37 @@
     <t>0.0127,0.0022,0.9882,0.0003</t>
   </si>
   <si>
-    <t>0.0774,0.0021,0.1376,0.6208</t>
-  </si>
-  <si>
-    <t>0.1989,0.0105,0.0693,0.6258</t>
-  </si>
-  <si>
-    <t>0.0882,0.0040,0.0481,0.8531</t>
-  </si>
-  <si>
-    <t>0.6527,0.0019,0.0104,0.2722</t>
-  </si>
-  <si>
-    <t>0.1137,0.0065,0.0456,0.8398</t>
-  </si>
-  <si>
-    <t>0.1072,0.0072,0.0621,0.8046</t>
-  </si>
-  <si>
-    <t>0.1913,0.0049,0.0795,0.5879</t>
-  </si>
-  <si>
-    <t>0.2291,0.0045,0.2135,0.1757</t>
-  </si>
-  <si>
-    <t>0.0184,0.0060,0.9168,0.0400</t>
-  </si>
-  <si>
-    <t>0.0585,0.0754,0.7031,0.1757</t>
-  </si>
-  <si>
-    <t>0.2251,0.0137,0.2234,0.3039</t>
+    <t>0.0775,0.0021,0.1379,0.6198</t>
+  </si>
+  <si>
+    <t>0.1992,0.0105,0.0695,0.6248</t>
+  </si>
+  <si>
+    <t>0.0883,0.0040,0.0482,0.8526</t>
+  </si>
+  <si>
+    <t>0.6530,0.0019,0.0105,0.2716</t>
+  </si>
+  <si>
+    <t>0.1138,0.0065,0.0457,0.8394</t>
+  </si>
+  <si>
+    <t>0.1073,0.0072,0.0623,0.8039</t>
+  </si>
+  <si>
+    <t>0.1916,0.0049,0.0796,0.5871</t>
+  </si>
+  <si>
+    <t>0.2292,0.0045,0.2140,0.1752</t>
+  </si>
+  <si>
+    <t>0.0184,0.0060,0.9169,0.0399</t>
+  </si>
+  <si>
+    <t>0.0586,0.0755,0.7032,0.1752</t>
+  </si>
+  <si>
+    <t>0.2252,0.0137,0.2238,0.3033</t>
   </si>
   <si>
     <t>0.0003,0.0010,0.9995,0.0001</t>
@@ -1495,7 +1501,7 @@
     <t>0.0002,0.0079,0.9992,0.0005</t>
   </si>
   <si>
-    <t>0.0088,0.0639,0.9755,0.0081</t>
+    <t>0.0088,0.0639,0.9756,0.0081</t>
   </si>
   <si>
     <t>0.0000,0.0002,0.9999,0.0000</t>
@@ -1510,40 +1516,40 @@
     <t>0.0017,0.0210,0.9950,0.0031</t>
   </si>
   <si>
-    <t>0.0919,0.0979,0.7541,0.1027</t>
-  </si>
-  <si>
-    <t>0.3445,0.0041,0.1704,0.3915</t>
-  </si>
-  <si>
-    <t>0.3573,0.0008,0.0817,0.4056</t>
-  </si>
-  <si>
-    <t>0.7662,0.0040,0.0294,0.1687</t>
-  </si>
-  <si>
-    <t>0.1411,0.0071,0.0788,0.6302</t>
-  </si>
-  <si>
-    <t>0.6979,0.0027,0.0096,0.2129</t>
-  </si>
-  <si>
-    <t>0.1590,0.0056,0.0839,0.6374</t>
-  </si>
-  <si>
-    <t>0.1432,0.0131,0.1007,0.6328</t>
-  </si>
-  <si>
-    <t>0.2449,0.0070,0.1754,0.2358</t>
-  </si>
-  <si>
-    <t>0.2052,0.0097,0.0438,0.7022</t>
-  </si>
-  <si>
-    <t>0.1848,0.0057,0.0381,0.7324</t>
-  </si>
-  <si>
-    <t>0.2096,0.0062,0.0910,0.5013</t>
+    <t>0.0917,0.0979,0.7546,0.1025</t>
+  </si>
+  <si>
+    <t>0.3447,0.0041,0.1708,0.3906</t>
+  </si>
+  <si>
+    <t>0.3575,0.0008,0.0818,0.4049</t>
+  </si>
+  <si>
+    <t>0.7662,0.0040,0.0295,0.1685</t>
+  </si>
+  <si>
+    <t>0.1413,0.0071,0.0789,0.6292</t>
+  </si>
+  <si>
+    <t>0.6979,0.0027,0.0096,0.2126</t>
+  </si>
+  <si>
+    <t>0.1592,0.0056,0.0841,0.6364</t>
+  </si>
+  <si>
+    <t>0.1436,0.0131,0.1008,0.6317</t>
+  </si>
+  <si>
+    <t>0.2451,0.0070,0.1757,0.2353</t>
+  </si>
+  <si>
+    <t>0.2057,0.0097,0.0439,0.7011</t>
+  </si>
+  <si>
+    <t>0.1851,0.0057,0.0382,0.7316</t>
+  </si>
+  <si>
+    <t>0.2097,0.0062,0.0912,0.5004</t>
   </si>
   <si>
     <t>0.0063,0.0523,0.9790,0.0075</t>
@@ -1558,34 +1564,34 @@
     <t>0.0153,0.0304,0.9688,0.0135</t>
   </si>
   <si>
-    <t>0.0154,0.0016,0.9837,0.0014</t>
-  </si>
-  <si>
-    <t>0.5844,0.0049,0.0671,0.2240</t>
-  </si>
-  <si>
-    <t>0.2444,0.0117,0.5258,0.0433</t>
+    <t>0.0153,0.0016,0.9837,0.0014</t>
+  </si>
+  <si>
+    <t>0.5840,0.0049,0.0673,0.2237</t>
+  </si>
+  <si>
+    <t>0.2444,0.0117,0.5261,0.0431</t>
   </si>
   <si>
     <t>0.0008,0.0028,0.9978,0.0022</t>
   </si>
   <si>
-    <t>0.5652,0.0007,0.0071,0.5834</t>
+    <t>0.5658,0.0007,0.0071,0.5826</t>
   </si>
   <si>
     <t>0.0022,0.0004,0.0020,0.9995</t>
   </si>
   <si>
-    <t>0.0091,0.0002,0.0044,0.9967</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0313,0.9988</t>
+    <t>0.0091,0.0002,0.0044,0.9966</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.0314,0.9988</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.0042,0.9999</t>
   </si>
   <si>
-    <t>0.7986,0.0025,0.0075,0.1693</t>
+    <t>0.7988,0.0025,0.0075,0.1691</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2005,7 @@
         <v>265</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2019,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,10 +2030,10 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2047,7 @@
         <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2061,7 @@
         <v>265</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,10 +2072,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2089,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2103,7 @@
         <v>265</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2117,7 @@
         <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2131,7 @@
         <v>265</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,10 +2156,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,10 +2170,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,10 +2184,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,10 +2212,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,10 +2226,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2237,7 +2243,7 @@
         <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,10 +2254,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,10 +2268,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2285,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,10 +2296,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,10 +2310,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,10 +2324,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,10 +2338,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,10 +2352,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,10 +2366,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2397,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,10 +2408,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,10 +2422,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,7 +2467,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,10 +2478,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2492,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,10 +2506,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,10 +2520,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,10 +2534,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2548,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,10 +2562,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,10 +2576,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2593,7 @@
         <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,10 +2604,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,10 +2618,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,10 +2632,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,10 +2646,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,10 +2660,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,10 +2674,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,10 +2688,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,10 +2702,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,10 +2716,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,10 +2730,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2747,7 @@
         <v>265</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,10 +2772,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,10 +2786,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2803,7 @@
         <v>265</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,10 +2814,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2828,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,10 +2842,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,10 +2856,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2870,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,10 +2884,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,10 +2898,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,10 +2912,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,10 +2940,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,10 +2954,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2968,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2982,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2996,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3010,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3091,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3108,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3122,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3136,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3150,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3164,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3178,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3195,7 @@
         <v>265</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3209,7 @@
         <v>265</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3237,7 @@
         <v>265</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3251,7 @@
         <v>265</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3279,7 @@
         <v>265</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3307,7 @@
         <v>265</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3335,7 @@
         <v>265</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3363,7 @@
         <v>265</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3391,7 @@
         <v>265</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,10 +3402,10 @@
         <v>259</v>
       </c>
       <c r="C104" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,10 +3416,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,10 +3430,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,10 +3458,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,10 +3472,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,10 +3486,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3497,7 +3503,7 @@
         <v>264</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3514,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,10 +3528,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,10 +3542,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,10 +3570,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,10 +3584,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3601,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,10 +3612,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,10 +3626,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,10 +3640,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,10 +3654,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,10 +3668,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,10 +3682,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,10 +3696,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3710,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,10 +3724,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3741,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3769,7 @@
         <v>265</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3811,7 @@
         <v>265</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3825,7 @@
         <v>265</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,10 +3836,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3850,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3864,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,10 +3878,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,10 +3892,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,10 +3920,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,10 +3934,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3965,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3973,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3987,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4018,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4035,7 @@
         <v>265</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4043,7 +4049,7 @@
         <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,10 +4060,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,10 +4074,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,10 +4102,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,10 +4116,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,10 +4130,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,10 +4144,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4175,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,10 +4214,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,10 +4256,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4273,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4287,7 @@
         <v>265</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,10 +4298,10 @@
         <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,10 +4326,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4343,7 @@
         <v>265</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4357,7 @@
         <v>265</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,10 +4368,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4385,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4399,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,10 +4410,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,10 +4424,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,10 +4438,10 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,10 +4452,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4469,7 @@
         <v>265</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,10 +4480,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,10 +4494,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,10 +4508,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,10 +4522,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,10 +4536,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4550,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,10 +4564,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,10 +4578,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,10 +4592,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,10 +4606,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,10 +4620,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,10 +4648,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,10 +4662,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,10 +4676,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,10 +4690,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4721,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,10 +4732,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,10 +4746,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,10 +4760,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4777,7 @@
         <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4791,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,10 +4816,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,10 +4830,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,10 +4844,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,10 +4858,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,10 +4872,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,10 +4886,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,10 +4900,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,10 +4914,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4931,7 @@
         <v>265</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4945,7 @@
         <v>265</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4959,7 @@
         <v>265</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4987,7 @@
         <v>265</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5001,7 @@
         <v>265</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5015,7 @@
         <v>265</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,10 +5026,10 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,10 +5040,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,10 +5054,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,10 +5068,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,10 +5082,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,10 +5096,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,10 +5110,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,10 +5124,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,10 +5138,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,10 +5152,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,10 +5166,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,10 +5180,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,10 +5194,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,10 +5208,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5239,7 @@
         <v>265</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5253,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5267,7 @@
         <v>265</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5281,7 @@
         <v>265</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,10 +5292,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5309,7 @@
         <v>265</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5323,7 @@
         <v>265</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5337,7 @@
         <v>265</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,10 +5348,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,10 +5362,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,10 +5376,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,10 +5390,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,10 +5404,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5421,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,10 +5432,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,10 +5446,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,10 +5460,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5499,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5513,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
